--- a/public/excel/product/Giá thép ống tôn mạ kẽm.xlsx
+++ b/public/excel/product/Giá thép ống tôn mạ kẽm.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="67">
   <si>
     <t xml:space="preserve">Tên</t>
   </si>
@@ -49,6 +49,9 @@
     <t xml:space="preserve">Loại</t>
   </si>
   <si>
+    <t xml:space="preserve">Lô hàng</t>
+  </si>
+  <si>
     <t xml:space="preserve">Thép ống mạ kẽm 21,2 x 1,1 x 6m</t>
   </si>
   <si>
@@ -56,6 +59,9 @@
   </si>
   <si>
     <t xml:space="preserve">Thép hình</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISM221</t>
   </si>
   <si>
     <t xml:space="preserve">Thép ống mạ kẽm 21,2 x 1,2 x 6m</t>
@@ -451,7 +457,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="39.43"/>
@@ -487,10 +493,13 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="3" t="n">
         <v>6</v>
@@ -511,15 +520,18 @@
         <v>55.592</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" s="8" t="n">
         <v>6</v>
@@ -540,15 +552,18 @@
         <v>60.352</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B4" s="8" t="n">
         <v>6</v>
@@ -569,15 +584,18 @@
         <v>69.702</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B5" s="8" t="n">
         <v>6</v>
@@ -598,15 +616,18 @@
         <v>74.292</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B6" s="8" t="n">
         <v>6</v>
@@ -627,15 +648,18 @@
         <v>87.893</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B7" s="8" t="n">
         <v>6</v>
@@ -656,15 +680,18 @@
         <v>70.722</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B8" s="8" t="n">
         <v>6</v>
@@ -685,15 +712,18 @@
         <v>88.913</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B9" s="8" t="n">
         <v>6</v>
@@ -714,15 +744,18 @@
         <v>94.863</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B10" s="8" t="n">
         <v>6</v>
@@ -743,15 +776,18 @@
         <v>112.543</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B11" s="8" t="n">
         <v>6</v>
@@ -772,15 +808,18 @@
         <v>89.593</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B12" s="8" t="n">
         <v>6</v>
@@ -801,15 +840,18 @@
         <v>113.053</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B13" s="8" t="n">
         <v>6</v>
@@ -830,15 +872,18 @@
         <v>120.704</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B14" s="8" t="n">
         <v>6</v>
@@ -859,15 +904,18 @@
         <v>143.484</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B15" s="8" t="n">
         <v>6</v>
@@ -888,15 +936,18 @@
         <v>113.733</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B16" s="8" t="n">
         <v>6</v>
@@ -917,15 +968,18 @@
         <v>143.654</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B17" s="8" t="n">
         <v>6</v>
@@ -946,15 +1000,18 @@
         <v>153.515</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B18" s="8" t="n">
         <v>6</v>
@@ -975,15 +1032,18 @@
         <v>141.614</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B19" s="8" t="n">
         <v>6</v>
@@ -1004,15 +1064,18 @@
         <v>164.395</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B20" s="8" t="n">
         <v>6</v>
@@ -1033,15 +1096,18 @@
         <v>175.785</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B21" s="8" t="n">
         <v>6</v>
@@ -1062,15 +1128,18 @@
         <v>209.616</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B22" s="8" t="n">
         <v>6</v>
@@ -1091,15 +1160,18 @@
         <v>231.887</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B23" s="8" t="n">
         <v>6</v>
@@ -1120,15 +1192,18 @@
         <v>265.038</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B24" s="8" t="n">
         <v>6</v>
@@ -1149,15 +1224,18 @@
         <v>286.798</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B25" s="8" t="n">
         <v>6</v>
@@ -1178,15 +1256,18 @@
         <v>172.215</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B26" s="8" t="n">
         <v>6</v>
@@ -1207,15 +1288,18 @@
         <v>219.646</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B27" s="8" t="n">
         <v>6</v>
@@ -1236,15 +1320,18 @@
         <v>242.937</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B28" s="8" t="n">
         <v>6</v>
@@ -1265,15 +1352,18 @@
         <v>277.788</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B29" s="8" t="n">
         <v>6</v>
@@ -1294,15 +1384,18 @@
         <v>206.046</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B30" s="8" t="n">
         <v>6</v>
@@ -1323,15 +1416,18 @@
         <v>220.326</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B31" s="8" t="n">
         <v>6</v>
@@ -1352,15 +1448,18 @@
         <v>262.998</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B32" s="8" t="n">
         <v>6</v>
@@ -1381,15 +1480,18 @@
         <v>291.219</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B33" s="8" t="n">
         <v>6</v>
@@ -1410,15 +1512,18 @@
         <v>333.21</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B34" s="8" t="n">
         <v>6</v>
@@ -1439,15 +1544,18 @@
         <v>360.921</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B35" s="8" t="n">
         <v>6</v>
@@ -1468,15 +1576,18 @@
         <v>429.433</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B36" s="8" t="n">
         <v>6</v>
@@ -1497,15 +1608,18 @@
         <v>456.463</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J36" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B37" s="8" t="n">
         <v>6</v>
@@ -1526,15 +1640,18 @@
         <v>279.658</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J37" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B38" s="8" t="n">
         <v>6</v>
@@ -1555,15 +1672,18 @@
         <v>334.23</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J38" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B39" s="8" t="n">
         <v>6</v>
@@ -1584,15 +1704,18 @@
         <v>370.271</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J39" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B40" s="8" t="n">
         <v>6</v>
@@ -1613,15 +1736,18 @@
         <v>418.042</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J40" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B41" s="8" t="n">
         <v>6</v>
@@ -1642,15 +1768,18 @@
         <v>424.162</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J41" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B42" s="8" t="n">
         <v>6</v>
@@ -1671,15 +1800,18 @@
         <v>547.926</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J42" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B43" s="8" t="n">
         <v>6</v>
@@ -1700,15 +1832,18 @@
         <v>327.6</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J43" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B44" s="8" t="n">
         <v>6</v>
@@ -1729,15 +1864,18 @@
         <v>391.692</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J44" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B45" s="8" t="n">
         <v>6</v>
@@ -1758,15 +1896,18 @@
         <v>434.193</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J45" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B46" s="8" t="n">
         <v>6</v>
@@ -1787,15 +1928,18 @@
         <v>497.605</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J46" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B47" s="8" t="n">
         <v>6</v>
@@ -1816,15 +1960,18 @@
         <v>539.596</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J47" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B48" s="8" t="n">
         <v>6</v>
@@ -1845,15 +1992,18 @@
         <v>602.158</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J48" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B49" s="8" t="n">
         <v>6</v>
@@ -1874,15 +2024,18 @@
         <v>645.509</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J49" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B50" s="8" t="n">
         <v>6</v>
@@ -1903,15 +2056,18 @@
         <v>505.765</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J50" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B51" s="8" t="n">
         <v>6</v>
@@ -1932,15 +2088,18 @@
         <v>561.017</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J51" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B52" s="8" t="n">
         <v>6</v>
@@ -1961,15 +2120,18 @@
         <v>643.299</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J52" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B53" s="8" t="n">
         <v>6</v>
@@ -1990,15 +2152,18 @@
         <v>698.041</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J53" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B54" s="8" t="n">
         <v>6</v>
@@ -2019,15 +2184,18 @@
         <v>807.252</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J54" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B55" s="8" t="n">
         <v>6</v>
@@ -2048,10 +2216,13 @@
         <v>833.875</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J55" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
